--- a/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent. Elle dit : je suis surprise. La casserole a fait le bruit. Maman dit : d'abord respirer. Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé. Francine dit : je veux comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
+          <t>Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent. Je suis surprise. La casserole a fait le bruit. D'abord respirer. Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé. Je veux comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent.
+narrateur|Je suis surprise.
+narrateur|La casserole a fait le bruit.
+maman|D'abord respirer.
+narrateur|Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé.
+enfant-f|Je veux comprendre. Maman sourit. Être surpris, on peut respirer.
+narrateur|Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Francine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Francine a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Francine range une cuillère. Maman ferme le placard.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Francine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Francine a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Francine range une cuillère. Maman ferme le placard.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Francine est surprise</t>
+          <t>Victorina et la casserole</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une casserole fait clang. Victorina est surprise. Elle souffle. Elle comprend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent. Je suis surprise. La casserole a fait le bruit. D'abord respirer. Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé. Je veux comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
+          <t>Le robinet goutte, tout doux. Tic. Tic. Le carrelage est un peu froid. Ça sent le cacao. Une tasse attend sur la table. La tasse est encore tiède. Une chaise est un peu de travers. Papa tourne la cuillère. La mousse fait des petits trous. Une serviette à pois attend. Le cacao sent bon. Victorina, tu as les pieds au sol ? Oui, maman. La tasse est tiède. En ce moment, maman ouvre un placard. Une casserole tombe. Clang. Victorina sent son cœur vite. Ses épaules sautent. Je suis surprise. D'abord respirer. Victorina souffle. Elle va respirer encore. Puis comprendre. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Victorina regarde. C'est la casserole. Rien n'est cassé. La casserole a fait le bruit. Je comprends. Être surpris, on peut respirer. Puis on cherche à comprendre. Victorina pose la main sur son ventre. Elle souffle encore. Maman range la casserole. Le métal fait un petit bruit. Tu as soufflé. Tu as regardé. Clang. Puis calme. On respire. On comprend. Victorina compte les gouttes. Tic. Tic. Le robinet goutte encore. La tasse reste tiède. Tu as nommé. Tu as soufflé. Je suis surprise. Puis calme. On cherche à comprendre. La serviette à pois reste pliée.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent.
-narrateur|Je suis surprise.
-narrateur|La casserole a fait le bruit.
+          <t>narrateur|Le robinet goutte, tout doux.
+narrateur|Tic. Tic.
+narrateur|Le carrelage est un peu froid.
+narrateur|Ça sent le cacao.
+narrateur|Une tasse attend sur la table.
+narrateur|La tasse est encore tiède.
+narrateur|Une chaise est un peu de travers.
+narrateur|Papa tourne la cuillère.
+narrateur|La mousse fait des petits trous.
+narrateur|Une serviette à pois attend.
+papa|Le cacao sent bon.
+maman|Victorina, tu as les pieds au sol ?
+enfant-f|Oui, maman.
+papa|La tasse est tiède.
+narrateur|En ce moment, maman ouvre un placard.
+narrateur|Une casserole tombe.
+narrateur|Clang.
+narrateur|Victorina sent son cœur vite.
+narrateur|Ses épaules sautent.
+enfant-f|Je suis surprise.
 maman|D'abord respirer.
-narrateur|Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé.
-enfant-f|Je veux comprendre. Maman sourit. Être surpris, on peut respirer.
-narrateur|Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Victorina souffle.
+narrateur|Elle va respirer encore.
+papa|Puis comprendre.
+maman|Tu as soufflé. Bravo.
+papa|Qu'est-ce que tu vois ?
+enfant-f|Je veux comprendre.
+narrateur|Victorina regarde.
+narrateur|C'est la casserole.
+maman|Rien n'est cassé.
+papa|La casserole a fait le bruit.
+enfant-f|Je comprends.
+maman|Être surpris, on peut respirer.
+papa|Puis on cherche à comprendre.
+narrateur|Victorina pose la main sur son ventre.
+narrateur|Elle souffle encore.
+narrateur|Maman range la casserole.
+narrateur|Le métal fait un petit bruit.
+papa|Tu as soufflé. Tu as regardé.
+enfant-f|Clang. Puis calme.
+maman|On respire. On comprend.
+narrateur|Victorina compte les gouttes.
+narrateur|Tic. Tic.
+narrateur|Le robinet goutte encore.
+narrateur|La tasse reste tiède.
+papa|Tu as nommé. Tu as soufflé.
+enfant-f|Je suis surprise. Puis calme.
+maman|On cherche à comprendre.
+narrateur|La serviette à pois reste pliée.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine,casserole</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Francine est surprise. Que fait-elle d'abord ?</t>
+          <t>Victorina est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1564,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Francine est surprise. Que fait-elle d'abord ?</t>
+          <t>narrateur|Victorina est surprise.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Francine a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Maman était là.</t>
+          <t>Victorina a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Tu as soufflé. Bravo. Tu as regardé la casserole. C'était la casserole. Rien n'était cassé. On souffle. On comprend. La casserole est à sa place. Plus de clang. Victorina pose la main sur son ventre. Le cacao sent encore bon. On laisse la tasse un peu ? Oui. Elle est tiède.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,10 +1737,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Francine a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorina a nommé : surprise.
+narrateur|Elle a respiré.
+narrateur|Elle a voulu comprendre.
+maman|Tu as soufflé. Bravo.
+papa|Tu as regardé la casserole.
+enfant-f|C'était la casserole.
+maman|Rien n'était cassé.
+papa|On souffle. On comprend.
+maman|La casserole est à sa place.
+enfant-f|Plus de clang.
+narrateur|Victorina pose la main sur son ventre.
+narrateur|Le cacao sent encore bon.
+papa|On laisse la tasse un peu ?
+enfant-f|Oui. Elle est tiède.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Francine range une cuillère. Maman ferme le placard.</t>
+          <t>Victorina range une cuillère. Maman ferme le placard. On boit le cacao ? Oui. Il est tiède. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La tasse attend. On remet la chaise ? Oui. Tout droit. Le robinet s'arrête. Le carrelage reste froid. Ça sent encore le cacao. On pose la cuillère ? Oui. Dans la tasse. Bravo, Victorina. La mousse retombe tout doux. Le cacao est encore tiède. Je souffle. Puis je bois.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1918,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Francine range une cuillère. Maman ferme le placard.</t>
+          <t>narrateur|Victorina range une cuillère.
+narrateur|Maman ferme le placard.
+papa|On boit le cacao ?
+enfant-f|Oui. Il est tiède.
+maman|Tu as nommé. Tu as soufflé.
+enfant-f|Je suis calme, maintenant.
+papa|La tasse attend.
+maman|On remet la chaise ?
+enfant-f|Oui. Tout droit.
+narrateur|Le robinet s'arrête.
+narrateur|Le carrelage reste froid.
+narrateur|Ça sent encore le cacao.
+papa|On pose la cuillère ?
+enfant-f|Oui. Dans la tasse.
+maman|Bravo, Victorina.
+narrateur|La mousse retombe tout doux.
+papa|Le cacao est encore tiède.
+enfant-f|Je souffle. Puis je bois.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le cacao était tiède. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2103,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais surprise. J'ai soufflé.
+maman|Tu as compris. Bravo.
+papa|Le cacao était tiède.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Francine est dans la cuisine. Maman ouvre un placard. Une casserole tombe. Clang. Francine sent son cœur vite. Ses épaules sautent. Elle dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. La casserole a fait le bruit. Maman dit : d'abord respirer. Francine souffle. Elle va respirer encore. Puis comprendre. Elle regarde. C'est la casserole. Rien n'est cassé. Francine dit : je veux comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre. Francine pose la main sur son ventre. Elle souffle encore. Maman range la casserole.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le robinet goutte, tout doux. Tic. Tic. Le carrelage est un peu froid. Ça sent le cacao. Une tasse attend sur la table. La tasse est encore tiède. Une chaise est un peu de travers. Papa tourne la cuillère. La mousse fait des petits trous. Une serviette à pois attend. Le cacao sent bon. Victorina, tu as les pieds au sol ? Oui, maman. La tasse est tiède. En ce moment, maman ouvre un placard. Une casserole tombe. Clang. Victorina sent son cœur vite. Ses épaules sautent. Je suis surprise. D'abord respirer. Victorina souffle. Elle va respirer encore. Puis comprendre. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Victorina regarde. C'est la casserole. Rien n'est cassé. La casserole a fait le bruit. Je comprends. Être surpris, on peut respirer. Puis on cherche à comprendre. Victorina pose la main sur son ventre. Elle souffle encore. Maman range la casserole. Le métal fait un petit bruit. Tu as soufflé. Tu as regardé. Clang. Puis calme. On respire. On comprend. Victorina compte les gouttes. Tic. Tic. Le robinet goutte encore. La tasse reste tiède. Tu as nommé. Tu as soufflé. Je suis surprise. Puis calme. On cherche à comprendre. La serviette à pois reste pliée.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Francine est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1568,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,7 +1597,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Francine a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Elle a respiré. Elle a voulu comprendre. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a nommé : surprise. Elle a respiré. Elle a voulu comprendre. Tu as soufflé. Bravo. Tu as regardé la casserole. C'était la casserole. Rien n'était cassé. On souffle. On comprend. La casserole est à sa place. Plus de clang. Victorina pose la main sur son ventre. Le cacao sent encore bon. On laisse la tasse un peu ? Oui. Elle est tiède.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1787,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Francine range une cuillère. Maman ferme le placard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range une cuillère. Maman ferme le placard. On boit le cacao ? Oui. Il est tiède. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La tasse attend. On remet la chaise ? Oui. Tout droit. Le robinet s'arrête. Le carrelage reste froid. Ça sent encore le cacao. On pose la cuillère ? Oui. Dans la tasse. Bravo, Victorina. La mousse retombe tout doux. Le cacao est encore tiède. Je souffle. Puis je bois.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1938,7 +1937,6 @@
 enfant-f|Je souffle. Puis je bois.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1963,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le cacao était tiède. L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le cacao était tiède.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le cacao était tiède.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,11 +2103,9 @@
         <is>
           <t>enfant-f|J'étais surprise. J'ai soufflé.
 maman|Tu as compris. Bravo.
-papa|Le cacao était tiède.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le cacao était tiède.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Francine, maman</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
